--- a/Carrier_Timely_Filing_Reference.xlsx
+++ b/Carrier_Timely_Filing_Reference.xlsx
@@ -322,19 +322,19 @@
     <t xml:space="preserve">365 days from DOS; 90 days as of 1/1/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">1 year from the date the claim was originally processed - most claim adjustments and reconsiderations run from the processing date, not the date of service</t>
+    <t xml:space="preserve">90 days from the date of service. A resubmission gets no extension - it must land inside the same window as the original claim, so a claim filed late in the window leaves very little room to correct it</t>
   </si>
   <si>
     <t xml:space="preserve">1 year from the original processing date for a reconsideration. Self-funded groups that customise their appeal procedure may use a 180 day window</t>
   </si>
   <si>
-    <t xml:space="preserve">AZ Blue - Claims and Remits and Appeals and Grievances (azblue.com/provider/resources)</t>
+    <t xml:space="preserve">Resubmission window supplied by the practice. The reconsideration window is from AZ Blue - Claims and Remits and Appeals and Grievances (azblue.com/provider/resources), which states that most claim adjustments and requests for reconsideration must be made within one year of the date the claim was originally processed</t>
   </si>
   <si>
     <t xml:space="preserve">Blue Cross Blue Shield of Arizona (BCBS AZ); Blue Cross Blue Shield of Arizona</t>
   </si>
   <si>
-    <t xml:space="preserve">Limit changed on 1 January 2026. Use 90 days for dates of service on or after 01/01/2026 and 365 days for earlier dates - see the 'Notes &amp; Sources' tab.</t>
+    <t xml:space="preserve">Initial filing limit changed on 1 January 2026. Use 90 days for dates of service on or after 01/01/2026 and 365 days for earlier dates. Resubmissions run on the same 90 day clock from the date of service and get no extension, so on this carrier the correction window closes with the filing window. The reconsideration route is the opposite: 1 year from the date the claim was originally processed. Reach for a reconsideration rather than a resubmission once the 90 days are gone - see the 'Notes &amp; Sources' tab.</t>
   </si>
   <si>
     <t xml:space="preserve">BCBS REGENCE</t>
@@ -907,10 +907,10 @@
     <t xml:space="preserve">The date of service / processed date split</t>
   </si>
   <si>
-    <t xml:space="preserve">Corrected claims counted from the processed date: AARP MA Choice / Medicare Complete, Aetna, AZ Priority Care, Banner Health &amp; Aetna, BCBS, Devoted, Medica, Medicare, Optum, TriWest, UHC Commercial, UHC Community, UHC Dual Complete, UHC MA, Veterans Admin (VA CCN) and Wellcare by Allwell. A denial late in the initial filing window still leaves a full corrected claim window on these carriers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrected claims counted from the date of service: AHCCCS, Ambetter, Amerigroup, AZ Complete, Banner University MA, Banner University Medicaid, Cigna, Health Choice Medicaid, Health Choice Pathway, Humana Commercial, Humana MA, Mercy Care Advantage, Mercy Care Medicaid, Oscar Health and Tricare East. On these the original filing clock never restarts, so a slow first pass eats the correction window. Amerigroup, Humana and Mercy Care Advantage fall here by way of the contract or resubmission route rather than a published corrected claim rule.</t>
+    <t xml:space="preserve">Corrected claims counted from the processed date: AARP MA Choice / Medicare Complete, Aetna, AZ Priority Care, Banner Health &amp; Aetna, Devoted, Medica, Medicare, Optum, TriWest, UHC Commercial, UHC Community, UHC Dual Complete, UHC MA, Veterans Admin (VA CCN) and Wellcare by Allwell. A denial late in the initial filing window still leaves a full corrected claim window on these carriers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrected claims counted from the date of service: AHCCCS, Ambetter, Amerigroup, AZ Complete, Banner University MA, Banner University Medicaid, BCBS, Cigna, Health Choice Medicaid, Health Choice Pathway, Humana Commercial, Humana MA, Mercy Care Advantage, Mercy Care Medicaid, Oscar Health and Tricare East. On these the original filing clock never restarts, so a slow first pass eats the correction window. Amerigroup, Humana and Mercy Care Advantage fall here by way of the contract or resubmission route rather than a published corrected claim rule.</t>
   </si>
   <si>
     <t xml:space="preserve">Appeals counted from the date of service: AHCCCS, AZ Complete, Banner University MA, Banner University Medicaid, Health Choice Medicaid, Mercy Care Advantage and Mercy Care Medicaid - the AHCCCS plans, which allow 12 months from the date of service with a 60 day fallback from the adverse action date on the remittance advice when the denial lands late in that window. Every other appeal window on this list runs from the processed date.</t>
@@ -919,7 +919,7 @@
     <t xml:space="preserve">Traps worth knowing</t>
   </si>
   <si>
-    <t xml:space="preserve">Cigna does not restart the clock for a corrected claim. The corrected claim stays subject to the 90 day timely filing provision in the agreement, counted from the date of service, even though the appeal window is 180 days from the remittance. An appeal that is resolved by filing a corrected claim does not extend that 90 days.</t>
+    <t xml:space="preserve">Two carriers give no extension at all for a corrected claim, and they are the two shortest correction windows on the sheet. Cigna keeps the corrected claim subject to the 90 day timely filing provision in the agreement, counted from the date of service, even though its appeal window is 180 days from the remittance; an appeal resolved by filing a corrected claim does not extend that 90 days. BCBS of Arizona works the same way at 90 days from the date of service. On both, a claim filed late in the window leaves almost no room to correct it.</t>
   </si>
   <si>
     <t xml:space="preserve">Medicare separates the two routes. A clerical error or omission goes through reopening - 1 year from the initial determination - and not through the appeals process at all. A redetermination is 120 days from receipt of the initial determination, and receipt is presumed 5 calendar days after the remittance advice date, so the working figure is 125 days from the RA.</t>
@@ -940,7 +940,7 @@
     <t xml:space="preserve">Aetna runs both windows from the determination date: 180 days to submit a corrected claim or reconsideration, then a further 60 days from the reconsideration decision for a formal appeal. State exceptions apply to fully insured members.</t>
   </si>
   <si>
-    <t xml:space="preserve">BCBS of Arizona allows 1 year from the original processing date for most claim adjustments and reconsiderations. That is a far longer window than the 90 day initial filing limit that took effect on 1 January 2026, so a 2026 timely filing denial is worth reviewing rather than writing off.</t>
+    <t xml:space="preserve">BCBS of Arizona runs two very different clocks and the choice between them matters more than on any other carrier here. A resubmission has 90 days from the date of service, the same window as the original claim. A claim adjustment or reconsideration has 1 year from the date the claim was originally processed. Once the 90 days are gone the resubmission route is closed but the reconsideration route is still open for months, so a 2026 timely filing denial is worth working as a reconsideration rather than writing off - BCBS is the second largest payer by volume in the 2026-S1 pending file.</t>
   </si>
   <si>
     <t xml:space="preserve">UnitedHealthcare allows 180 calendar days from the original remittance date to correct a claim, but that window is capped by the filing limit in the agreement counted from the date of service - whichever closes first governs. On the 90 day UHC products that cap usually bites well before the 180 days does. Include every originally billed line on the correction, not just the line being fixed, or the omitted services are recovered as an overpayment.</t>
@@ -970,7 +970,7 @@
     <t xml:space="preserve">Sources and method</t>
   </si>
   <si>
-    <t xml:space="preserve">Every figure in columns B-M was taken from the carrier's own provider manual, provider portal page or, for Medicare, the CMS Claims Processing Manual, with two exceptions supplied by the practice: the Devoted windows and the Humana Gold Plus HMO appeal window on the Humana MA row. Column N names the source for the corrected claim and appeal figures row by row; the initial limits came from the carrier list supplied by the practice and, where that list was blank, from the carrier document named in the notes column. No figure was carried across from a related product.</t>
+    <t xml:space="preserve">Every figure in columns B-M was taken from the carrier's own provider manual, provider portal page or, for Medicare, the CMS Claims Processing Manual, with three exceptions supplied by the practice: the Devoted windows, the Humana Gold Plus HMO appeal window on the Humana MA row, and the BCBS resubmission window. Column N names the source for the corrected claim and appeal figures row by row; the initial limits came from the carrier list supplied by the practice and, where that list was blank, from the carrier document named in the notes column. No figure was carried across from a related product.</t>
   </si>
   <si>
     <t xml:space="preserve">Direct document downloads were blocked in the environment this research was run from, so the figures were read from the carriers' published pages through search rather than from locally saved PDFs. Rows marked 'Verify vs manual' are the ones where the published wording was general, varied by state, or came from a document written for another market, and the Arizona specific figure should be pulled from the manual before a claim is worked against it.</t>
@@ -982,7 +982,7 @@
     <t xml:space="preserve">Corrected claim and appeal windows are contract sensitive in the same way initial filing limits are. Where a contract and a provider manual disagree, the contract governs. Re-confirm before writing off a claim as untimely.</t>
   </si>
   <si>
-    <t xml:space="preserve">Corrected claim and appeal columns compiled 12 August 2026, and the remaining initial, corrected claim and appeal gaps filled on the same date. The Devoted windows and the Humana Gold Plus HMO appeal window were supplied by the practice; every other figure came from the carrier document named in column N or the notes column. No claim, patient or payment data is included in this workbook.</t>
+    <t xml:space="preserve">Corrected claim and appeal columns compiled 12 August 2026, and the remaining initial, corrected claim and appeal gaps filled on the same date. The Devoted windows, the Humana Gold Plus HMO appeal window and the BCBS resubmission window were supplied by the practice; every other figure came from the carrier document named in column N or the notes column. No claim, patient or payment data is included in this workbook.</t>
   </si>
 </sst>
 </file>
@@ -2289,10 +2289,10 @@
         <v>98</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>24</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B29" s="24" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$H$5:$H$40,"Date of service")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B30" s="24" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$H$5:$H$40,"Processed date")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/Carrier_Timely_Filing_Reference.xlsx
+++ b/Carrier_Timely_Filing_Reference.xlsx
@@ -85,567 +85,567 @@
     <t xml:space="preserve">AARP MA CHOICE / MEDICARE COMPLETE</t>
   </si>
   <si>
-    <t xml:space="preserve">Not documented</t>
+    <t xml:space="preserve">90 days from DOS</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
+    <t xml:space="preserve">Confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days from the processed date. This plan does not follow the general UnitedHealthcare rule of 180 days from the original remittance - it carries its own, longer window. Include every originally billed line on the correction, not just the line being fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processed date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days from the processed date, for reconsiderations and appeals alike. This plan does not run the general UnitedHealthcare two step budget, where 12 months from the EOB or PRA has to cover reconsideration and appeal together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplied by the practice for AARP Medicare Advantage from UHC AZ-0003 (HMO-POS), plan type Health Maintenance Organization (HMO) - Medicare Risk. These plan specific figures supersede the general UnitedHealthcare guidance at uhcprovider.com, which sets 180 days from the original remittance for a corrected claim and one 12 month budget covering reconsideration then appeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AARP MedicareComplete (SecureHorizons &amp; Oxford Network); AARP United Healthcare; AARP Medicare Advantage from UHC AZ-0003 (HMO-POS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figures are for AARP Medicare Advantage from UHC AZ-0003 (HMO-POS), plan type HMO - Medicare Risk, supplied by the practice. Administered by UnitedHealthcare but the plan carries its own windows rather than the general UHC ones: 365 days from the processed date to correct and 365 to appeal, against the 180 day correction window and the shared 12 month two step budget that the other UHC rows carry. The tight part is the front end - 90 days from the date of service to get the claim in, then a full year of room once it has been processed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AETNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 days per contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 days from the date of determination, unless the provider agreement says otherwise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconsideration 180 calendar days from the claim decision; formal appeal 60 calendar days from the reconsideration decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aetna - Disputes and appeals overview and Provider appeals (aetna.com/health-care-professionals/disputes-appeals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aetna; Aetna Legacy; Aetna Medicare HMO; Aetna Medicare PPO; Aetna Senior Supplemental (AESSI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per contract rather than provider manual, so the limit is specific to our agreement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCCCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 months from the date of service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 months from the date of service to resubmit and reach clean claim status, provided the original claim was received inside the 6 month window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date of service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 months from the date of service. If the denial lands within 60 days of that deadline, 60 days from the adverse action date printed on the remittance advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCCCS - Claim Resubmission and Reconsideration Process and Provider Claim Disputes (azahcccs.gov/PlansProviders/RatesAndBilling/FFS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arizona Medicaid fee for service. An initial claim must be received within 6 months of the date of service, except where retro-eligibility applies; claims received later are denied. Secondary claims must meet the same 6 month test. The limit is stated in months - column C carries 180 days so the row sorts and calculates, but count 6 calendar months from the date of service for the real deadline. AHCCCS-contracted plans (Mercy Care, Health Choice, Banner University, UHC Community, AZ Complete) are listed separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMBETTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days from the date of service. The original claim reference number must be on the resubmission or it is treated as a new claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconsideration (level I) 180 days from the date on the original EOP or denial; claim dispute (level II) only after an unsatisfactory reconsideration response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify vs manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambetter from Arizona Complete Health - Provider and Billing Manual (azcompletehealth.com); Ambetter Provider Claims and Payments FAQ (ambetterhealth.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centene marketplace product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERIGROUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must fall inside the initial filing limit and carry the corrected claim frequency code; a corrected claim filed inside that limit rebuts a timely filing denial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify vs contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconsideration up to 24 months from the EOP date (shorter in some states); payment appeal 60 calendar days from the EOP or the reconsideration determination notice; second level 30 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amerigroup - Claims Timely Filing and Corrected Claims reimbursement policies; Payment appeal timely filing limit update (provider.amerigroup.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No matching payer name in the 2026-S1 pending file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ COMPLETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days from the date of service. The original claim reference number must be on the resubmission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconsideration 12 months from the date of service, reviewed within 60 days; formal provider claim dispute follows an unsuccessful reconsideration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arizona Complete Health - Provider Manual Finance/Billing and Grievance and Appeal System; Medicaid Provider Claim Resolution Process (azcompletehealth.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arizona Complete Health (Centene)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ PRIORITY CARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No separate corrected claim window published. A claim decision you disagree with goes through the dispute route below, which allows 365 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 calendar days of the initial claim decision. File on the Provider Dispute Resolution Request (PDR) form through the AZ Connect portal, with the original claim, EOB, authorisation and records</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arizona Priority Care - Claims Submission and Appeals, rev. 8 August 2025, and Claims and Payments toolkit (azprioritycare.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arizona Priority Care Plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest limit on this list together with BHN and Devoted - work these denials first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANNER HEALTH &amp; AETNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 days from the date of the initial decision, unless state regulation or the organisational provider contract allows longer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 days from the date of the initial decision, unless state regulation or the organisational provider contract allows longer. Decision issued within 60 calendar days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Aetna - Dispute &amp; Appeals Process Quick Reference Guide (banneraetna.com/en/health-care-professionals/dispute-and-appeals-overview); Aetna - Disputes and appeals overview (aetna.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Health &amp; Aetna Health Insurance Company; Banner Aetna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint venture product; separate from the Aetna and BHN rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANNER HEALTH NETWORK (BHN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not documented as a separate window. Mark the claim "Resubmission" or set the resubmission box on an electronic claim</t>
+  </si>
+  <si>
     <t xml:space="preserve">Needs research</t>
   </si>
   <si>
+    <t xml:space="preserve">Not documented as a separate provider claim dispute window on the open site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Health Network 2026 Provider Resource Manual v8.0, 10 December 2025 (bannerhealthnetwork.com/Document/1142) - could not be retrieved, pull the claims chapter directly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Health Physician Hospital Organization Plan Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest limit on this list together with AZ Priority Care and Devoted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANNER MEDICARE ADVANTAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65 calendar days from the date printed on the written coverage decision denial notice. This is the published coverage decision window - confirm the provider claim payment dispute window in the provider manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Medicare Advantage - Appeals (bannerhealth.com/medicare/members/resources/g-and-a/appeals); 2026 Provider Manual effective 05/15/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Medicare Advantage Prime HMO (BMAH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANNER UNIVERSITY MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 months from the date of service, under the AHCCCS resubmission rule. Mark the claim "Resubmission" or set the resubmission box on an electronic claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 months from the date of service. If the denial lands within 60 days of that deadline, 60 days from the adverse action date on the remittance advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Health Plans - Claims and Payments (bannerhealth.com/bhpprovider/resources/claims); AHCCCS agreement YH23-0010 identifying Banner - University Care Advantage as the D-SNP; AHCCCS Claim Resubmission and Reconsideration Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs to be verified against the contract.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANNER UNIVERSITY MEDICAID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconsideration 12 months from the date of service. If the denial lands within 60 days of that deadline, 60 days from the adverse action date on the remittance advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner Health Plans - AHCCCS Complete Care Provider Manual and Claims pages (bannerhealth.com/bhpprovider/resources/claims); AHCCCS Claim Resubmission and Reconsideration Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner University Family Care - Arizona Long Term Care System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days from DOS; 90 days as of 1/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 days from the date of service. A resubmission gets no extension - it must land inside the same window as the original claim, so a claim filed late in the window leaves very little room to correct it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 year from the original processing date for a reconsideration. Self-funded groups that customise their appeal procedure may use a 180 day window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resubmission window supplied by the practice. The reconsideration window is from AZ Blue - Claims and Remits and Appeals and Grievances (azblue.com/provider/resources), which states that most claim adjustments and requests for reconsideration must be made within one year of the date the claim was originally processed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Cross Blue Shield of Arizona (BCBS AZ); Blue Cross Blue Shield of Arizona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial filing limit changed on 1 January 2026. Use 90 days for dates of service on or after 01/01/2026 and 365 days for earlier dates. Resubmissions run on the same 90 day clock from the date of service and get no extension, so on this carrier the correction window closes with the filing window. The reconsideration route is the opposite: 1 year from the date the claim was originally processed. Reach for a reconsideration rather than a resubmission once the 90 days are gone - see the 'Notes &amp; Sources' tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCBS REGENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days from DOS (90 days as of 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not documented as a separate window on the open provider site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 days from the date of the initial adverse determination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regence - Pricing disputes and appeals and Claims submission (regence.com/provider/claims-payment). The 180 day figure is not stated on the open provider pages; confirm against the provider administrative manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same 2026 reduction as BCBS. Use 90 days for 2026 dates of service and 365 days for earlier dates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIGNA / CIGNA MEDICARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No automatic extension. A corrected claim stays subject to the timely filing provision in the Cigna agreement, so the 90 day window from the date of service still governs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 calendar days from the date of the initial payment or denial notice, or from the date of the last payment adjustment. Reconsideration also 180 days from the claim payment date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cigna Healthcare - Appeals and Disputes and Appeal Policy and Procedures for Health Care Professionals (cigna.com/health-care-providers/coverage-and-claims/appeals-disputes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealthSpring Medicare Advantage; CIGNA HealthSprings; Cigna Medicare Advantage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same limit for the commercial and Medicare Advantage products.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEVOTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 year from the claim processed date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 days from the latest processed date, filed as a dispute on the provider portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplied by the practice. The Devoted provider manual names its timely filing and payment dispute sections but does not publish the day counts openly, so this is the practice figure rather than a published one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devoted Health Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest limit on this list together with AZ Priority Care and BHN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEALTH CHOICE MEDICAID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 months (not primary) or 7 months (primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 months from the date of service, for contracted and non-contracted providers alike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The claim must be timely - 1 year from the date of service or 60 days from the date of the last adverse action - to be eligible for review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCBSAZ Health Choice - Provider Manual and Claims (azblue.com/medicaid/providers/claims; healthchoiceaz.com/providers/provider-manual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Choice Arizona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two limits - 6 months when Health Choice is not the primary payer, 7 months when it is. Stated in months, not days, so count calendar months from the date of service. Column C carries 180 days, the shorter of the two, so the row never calculates a deadline later than the rule allows; add a month where Health Choice is primary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEALTH CHOICE PATHWAY (HEALTH CHOICE GENERATIONS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A corrected claim is treated as a new claim for an initial organisation determination, not as an appeal. It must be timely - 1 year from the date of service or 60 days from the last adverse action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard reconsideration 60 calendar days from the date of denial; second level grievance 60 calendar days after receipt of the first level determination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Choice Pathway - Providers Claims (azblue.com/health-choice-pathway/providers/providers-claims)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Choice Pathway (Health Choice Generations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stated in months, not days - count 6 calendar months from the date of service (roughly 180-184 days). Column C carries 180 days, the conservative end of that range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUMANA COMMERCIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 days from DOS (physicians); 90 days from DOS (ancillary providers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No separate window published - the corrected claim rides the initial filing limit from the date of service, so the shorter 90 day ancillary figure governs unless the rendering provider is confirmed as a physician, which allows 180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 2 appeal 60 days from the level 1 denial; level 3 four months from the level 2 denial. The level 1 window is set by the medical policy or the provider agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humana - Reconsiderations and appeals and Claim payment inquiry resolution guide (provider.humana.com/coverage-claims/payment-integrity/reconsiderations-appeals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two limits depending on provider type. Column C carries 90 days, the ancillary figure, so the row never calculates a deadline later than the rule allows. Confirm the rendering provider is a physician before relying on the longer 180 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUMANA MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 months from the processed date to file an appeal. Humana's published escalation ladder then runs on top: level 2 appeal 60 days from the level 1 denial, level 3 four months from the level 2 denial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplied by the practice for Humana Gold Plus HMO. Humana publishes the level 2 and level 3 timers (provider.humana.com/coverage-claims/payment-integrity/reconsiderations-appeals) but not the level 1 filing window, which is set by the plan or the provider agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humana Gold Plus HMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same initial filing split as Humana commercial - column C carries the 90 day ancillary figure, so confirm the rendering provider is a physician before relying on 180 days. The appeal window is the opposite story and the longest on this sheet: 18 months from the processed date, against 90 days to get the claim in. A Humana Gold Plus timely filing denial is worth reviewing long after the filing window itself has closed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEDICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 days from DOS; 180 days from the Medicare payment date for Select Solution and Prime Solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within the filing limit in the agreement, but the clock starts on the date Medica notified you the claim failed processing or was denied. Where the rejection was Medica error, up to 1 year from the Confirmation Report run date or the EOP date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 months from the processing date. For provider liability denials, 12 months from the check date on the PRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medica - Claim Adjustment/Appeal Guidelines and Timely Filing and Late Claims Policy (partner.medica.com/providers/medica-administrative-manual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In network original claims must reach the designated claims address within 180 days of the date of service, or the discharge date for inpatient. On Medica Select Solution and Prime Solution with Medicare primary, the 180 days runs from the payment date on the explanation of Medicare benefits instead. The provider agreement can set a different limit and governs where it does.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEDICARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reopening to correct a clerical error or omission - 1 year from the date of the initial determination. Minor errors go through reopening, not the appeals process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redetermination - 120 days from receipt of the initial determination. Receipt is presumed 5 calendar days after the date on the remittance advice, so the MAC allows 125 days from the RA date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMS - Medicare Claims Processing Manual Chapter 34, Reopening and Revision of Claim Determinations; First Level of Appeal: Redetermination by a Medicare Contractor (cms.gov)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicare Part B Arizona *; DME Region D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One calendar year from the date of service, set by statute rather than by contract. Largest payer in the 2026-S1 pending file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCY CARE ADVANTAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 days from DOS or eligibility posting, whichever is later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resubmission is the only route - contracted providers have no claim dispute rights on this product. Mark the claim "Attention: Resubmissions" so it is not denied as a duplicate. The Advantage manual publishes no separate window, so the AHCCCS resubmission parameter of 12 months from the date of service is applied here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 months from the date of service, applied from the AHCCCS parameter at the practice's direction. The published Advantage manual takes the opposite position - it states that contracted providers have no claim dispute rights on this product and directs a disputed claim back through resubmission - so confirm the route with Mercy Care before filing a dispute rather than a resubmission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercy Care Advantage Provider Manual, January 2026 (mercycareaz.org/providers/provider-manual.html)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercy Care Health Plan Advantage (AHCCCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New claims must be filed within 150 days of the date of service or the eligibility posting date, whichever is later - a shorter window than the 365 days Mercy Care Medicaid allows. Corrected claim and dispute windows follow the AHCCCS parameter of 12 months from the date of service, the same as Mercy Care Medicaid, applied at the practice's direction. Be aware the published Advantage manual says contracted providers have no claim dispute rights here and routes disputed claims through resubmission instead, so a dispute may be refused on that basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCY CARE MEDICAID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days from the date of service or the eligibility posting date, whichever is later. If a claim is recouped, a further 60 days from the recoupment date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim disputes: 12 months from the date of service, 12 months after the eligibility posting date, or 60 days after the date of a timely claim submission - whichever is less</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercy Care - Claims Processing Manual and Provider Manual; Claim Dispute Reminder notices (mercycareaz.org/providers/claims.html)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC); Mercy Care RBHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No separate window published. Resubmit with claim frequency code 7 and the payer claim control number; a disputed decision goes through the PDR route below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 calendar days of the payment or denial, on the Provider Dispute Resolution Request (PDR) form or through the Optum Pro portal. Outcome issued within 45 working days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optum Care - Claims Provider Manual and Arizona Provider Dispute Resolution Request form (optum.com; business.optum.com). The 365 day PDR window is Optum's standard across markets; it is published explicitly in the California AB 1455 dispute notices, not in an Arizona specific document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSCAR HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No separate window - the corrected claim must land inside the 180 day filing limit from the date of service. Submit the entire claim as a replacement with frequency code 7 (CMS 1500 box 22) or type of bill xx7 (UB-04), carrying the original payer claim ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 calendar days after notice of the adverse decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar Health - 2026 Provider Manual effective 01/01/26 and Claims Disputes Provider Form (hioscar.com/providers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDIRECT HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not documented - third party administrator, the plan document sets the limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not documented - third party administrator, the window comes from the underlying plan document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not documented - a formal claim appeal is filed on their online appeal form, but no window is published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirect Health - Provider Portal and claims information (redirecthealth.com). No filing windows published; claims questions to Claims@RedirectAdmin.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirect Health Administration LLC administers self-funded plans, so the filing limit comes from the underlying plan document rather than from a single Redirect policy. A clean claim is paid within 45 business days. Claim questions go to Claims@RedirectAdmin.com; appeals are filed on their online appeal form. No filing windows are published - request them from the plan administrator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRICARE EAST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 year from the date of service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must fall inside the 1 year claim filing deadline. A corrected claim is not an appeal and is filed separately to the corrected claims address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 days from the date on the explanation of benefits. Corrected claims are among the issues that are not appealable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humana Military - TRICARE Provider Handbook East Region and Claims pages (humanamilitary.com/provider/claims); TRICARE - How to Submit a Claim Appeal (tricare.mil)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administered by Humana Military. All claims for benefits must be filed no later than one year after the date services were provided. Note the pending file shows Tricare West and Tricare for Life, not Tricare East - confirm which region we actually bill, as the West region contractor changed on 1 January 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIWEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 days of the last processed claim determination date. The corrected claim completely replaces the previously filed claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconsideration 90 days of the original claim processed date. Forms filed outside that window are denied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TriWest VA CCN - Billing and Claims and Provider Claims Reconsideration (vaccn.triwest.com/en/provider)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIWEST VA CCN CLAIMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TriWest administers VA Community Care Network Region 4; claims post under the same payer name as the VA CCN row below, so check which limit the claim was billed under.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UHC COMMERCIAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">180 calendar days from the original remittance date. The corrected claim must also fall inside the filing window in the agreement counted from the date of service, so whichever window closes first governs. Include every originally billed line, not just the line being corrected</t>
   </si>
   <si>
-    <t xml:space="preserve">Processed date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the EOB / PRA to complete reconsideration then appeal (contracted). Non-contracted Medicare Advantage: 120 days from the original claim determination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify vs contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnitedHealthcare - Pre- and post-service appeals and reconsiderations (uhcprovider.com/en/claims-payments-billing/appeals.html); Medicare Advantage non-contracted care provider dispute and appeal rights (uhcprovider.com)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AARP MedicareComplete (SecureHorizons &amp; Oxford Network); AARP United Healthcare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No limit supplied. Administered by UnitedHealthcare - confirm whether the UHC Medicare Advantage limit (90 days) applies or whether the plan carries its own.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AETNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120 days per contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 days from the date of determination, unless the provider agreement says otherwise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconsideration 180 calendar days from the claim decision; formal appeal 60 calendar days from the reconsideration decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aetna - Disputes and appeals overview and Provider appeals (aetna.com/health-care-professionals/disputes-appeals)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aetna; Aetna Legacy; Aetna Medicare HMO; Aetna Medicare PPO; Aetna Senior Supplemental (AESSI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per contract rather than provider manual, so the limit is specific to our agreement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCCCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 months from the date of service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provider manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the date of service to resubmit and reach clean claim status, provided the original claim was received inside the 6 month window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date of service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the date of service. If the denial lands within 60 days of that deadline, 60 days from the adverse action date printed on the remittance advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCCCS - Claim Resubmission and Reconsideration Process and Provider Claim Disputes (azahcccs.gov/PlansProviders/RatesAndBilling/FFS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Medicaid fee for service. An initial claim must be received within 6 months of the date of service, except where retro-eligibility applies; claims received later are denied. Secondary claims must meet the same 6 month test. The limit is stated in months - column C carries 180 days so the row sorts and calculates, but count 6 calendar months from the date of service for the real deadline. AHCCCS-contracted plans (Mercy Care, Health Choice, Banner University, UHC Community, AZ Complete) are listed separately.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMBETTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 days from the date of service. The original claim reference number must be on the resubmission or it is treated as a new claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconsideration (level I) 180 days from the date on the original EOP or denial; claim dispute (level II) only after an unsatisfactory reconsideration response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify vs manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ambetter from Arizona Complete Health - Provider and Billing Manual (azcompletehealth.com); Ambetter Provider Claims and Payments FAQ (ambetterhealth.com)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centene marketplace product.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMERIGROUP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must fall inside the initial filing limit and carry the corrected claim frequency code; a corrected claim filed inside that limit rebuts a timely filing denial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconsideration up to 24 months from the EOP date (shorter in some states); payment appeal 60 calendar days from the EOP or the reconsideration determination notice; second level 30 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amerigroup - Claims Timely Filing and Corrected Claims reimbursement policies; Payment appeal timely filing limit update (provider.amerigroup.com)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No matching payer name in the 2026-S1 pending file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ COMPLETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 days from the date of service. The original claim reference number must be on the resubmission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconsideration 12 months from the date of service, reviewed within 60 days; formal provider claim dispute follows an unsuccessful reconsideration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Complete Health - Provider Manual Finance/Billing and Grievance and Appeal System; Medicaid Provider Claim Resolution Process (azcompletehealth.com)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Complete Health (Centene)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ PRIORITY CARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No separate corrected claim window published. A claim decision you disagree with goes through the dispute route below, which allows 365 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 calendar days of the initial claim decision. File on the Provider Dispute Resolution Request (PDR) form through the AZ Connect portal, with the original claim, EOB, authorisation and records</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Priority Care - Claims Submission and Appeals, rev. 8 August 2025, and Claims and Payments toolkit (azprioritycare.com)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Priority Care Plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest limit on this list together with BHN and Devoted - work these denials first.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANNER HEALTH &amp; AETNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 days from the date of the initial decision, unless state regulation or the organisational provider contract allows longer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 days from the date of the initial decision, unless state regulation or the organisational provider contract allows longer. Decision issued within 60 calendar days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Aetna - Dispute &amp; Appeals Process Quick Reference Guide (banneraetna.com/en/health-care-professionals/dispute-and-appeals-overview); Aetna - Disputes and appeals overview (aetna.com)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Health &amp; Aetna Health Insurance Company; Banner Aetna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joint venture product; separate from the Aetna and BHN rows.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANNER HEALTH NETWORK (BHN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not documented as a separate window. Mark the claim "Resubmission" or set the resubmission box on an electronic claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not documented as a separate provider claim dispute window on the open site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Health Network 2026 Provider Resource Manual v8.0, 10 December 2025 (bannerhealthnetwork.com/Document/1142) - could not be retrieved, pull the claims chapter directly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Health Physician Hospital Organization Plan Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest limit on this list together with AZ Priority Care and Devoted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANNER MEDICARE ADVANTAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65 calendar days from the date printed on the written coverage decision denial notice. This is the published coverage decision window - confirm the provider claim payment dispute window in the provider manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Medicare Advantage - Appeals (bannerhealth.com/medicare/members/resources/g-and-a/appeals); 2026 Provider Manual effective 05/15/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Medicare Advantage Prime HMO (BMAH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANNER UNIVERSITY MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the date of service, under the AHCCCS resubmission rule. Mark the claim "Resubmission" or set the resubmission box on an electronic claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the date of service. If the denial lands within 60 days of that deadline, 60 days from the adverse action date on the remittance advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Health Plans - Claims and Payments (bannerhealth.com/bhpprovider/resources/claims); AHCCCS agreement YH23-0010 identifying Banner - University Care Advantage as the D-SNP; AHCCCS Claim Resubmission and Reconsideration Process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs to be verified against the contract.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANNER UNIVERSITY MEDICAID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconsideration 12 months from the date of service. If the denial lands within 60 days of that deadline, 60 days from the adverse action date on the remittance advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner Health Plans - AHCCCS Complete Care Provider Manual and Claims pages (bannerhealth.com/bhpprovider/resources/claims); AHCCCS Claim Resubmission and Reconsideration Process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banner University Family Care - Arizona Long Term Care System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 days from DOS; 90 days as of 1/1/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 days from the date of service. A resubmission gets no extension - it must land inside the same window as the original claim, so a claim filed late in the window leaves very little room to correct it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 year from the original processing date for a reconsideration. Self-funded groups that customise their appeal procedure may use a 180 day window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resubmission window supplied by the practice. The reconsideration window is from AZ Blue - Claims and Remits and Appeals and Grievances (azblue.com/provider/resources), which states that most claim adjustments and requests for reconsideration must be made within one year of the date the claim was originally processed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue Cross Blue Shield of Arizona (BCBS AZ); Blue Cross Blue Shield of Arizona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initial filing limit changed on 1 January 2026. Use 90 days for dates of service on or after 01/01/2026 and 365 days for earlier dates. Resubmissions run on the same 90 day clock from the date of service and get no extension, so on this carrier the correction window closes with the filing window. The reconsideration route is the opposite: 1 year from the date the claim was originally processed. Reach for a reconsideration rather than a resubmission once the 90 days are gone - see the 'Notes &amp; Sources' tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCBS REGENCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 days from DOS (90 days as of 2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not documented as a separate window on the open provider site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 days from the date of the initial adverse determination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regence - Pricing disputes and appeals and Claims submission (regence.com/provider/claims-payment). The 180 day figure is not stated on the open provider pages; confirm against the provider administrative manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same 2026 reduction as BCBS. Use 90 days for 2026 dates of service and 365 days for earlier dates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIGNA / CIGNA MEDICARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 days from DOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No automatic extension. A corrected claim stays subject to the timely filing provision in the Cigna agreement, so the 90 day window from the date of service still governs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 calendar days from the date of the initial payment or denial notice, or from the date of the last payment adjustment. Reconsideration also 180 days from the claim payment date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cigna Healthcare - Appeals and Disputes and Appeal Policy and Procedures for Health Care Professionals (cigna.com/health-care-providers/coverage-and-claims/appeals-disputes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HealthSpring Medicare Advantage; CIGNA HealthSprings; Cigna Medicare Advantage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same limit for the commercial and Medicare Advantage products.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEVOTED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 year from the claim processed date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 days from the latest processed date, filed as a dispute on the provider portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplied by the practice. The Devoted provider manual names its timely filing and payment dispute sections but does not publish the day counts openly, so this is the practice figure rather than a published one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devoted Health Plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest limit on this list together with AZ Priority Care and BHN.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEALTH CHOICE MEDICAID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 months (not primary) or 7 months (primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the date of service, for contracted and non-contracted providers alike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The claim must be timely - 1 year from the date of service or 60 days from the date of the last adverse action - to be eligible for review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCBSAZ Health Choice - Provider Manual and Claims (azblue.com/medicaid/providers/claims; healthchoiceaz.com/providers/provider-manual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health Choice Arizona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two limits - 6 months when Health Choice is not the primary payer, 7 months when it is. Stated in months, not days, so count calendar months from the date of service. Column C carries 180 days, the shorter of the two, so the row never calculates a deadline later than the rule allows; add a month where Health Choice is primary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEALTH CHOICE PATHWAY (HEALTH CHOICE GENERATIONS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A corrected claim is treated as a new claim for an initial organisation determination, not as an appeal. It must be timely - 1 year from the date of service or 60 days from the last adverse action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard reconsideration 60 calendar days from the date of denial; second level grievance 60 calendar days after receipt of the first level determination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health Choice Pathway - Providers Claims (azblue.com/health-choice-pathway/providers/providers-claims)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health Choice Pathway (Health Choice Generations)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stated in months, not days - count 6 calendar months from the date of service (roughly 180-184 days). Column C carries 180 days, the conservative end of that range.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUMANA COMMERCIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 days from DOS (physicians); 90 days from DOS (ancillary providers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No separate window published - the corrected claim rides the initial filing limit from the date of service, so the shorter 90 day ancillary figure governs unless the rendering provider is confirmed as a physician, which allows 180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 2 appeal 60 days from the level 1 denial; level 3 four months from the level 2 denial. The level 1 window is set by the medical policy or the provider agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humana - Reconsiderations and appeals and Claim payment inquiry resolution guide (provider.humana.com/coverage-claims/payment-integrity/reconsiderations-appeals)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two limits depending on provider type. Column C carries 90 days, the ancillary figure, so the row never calculates a deadline later than the rule allows. Confirm the rendering provider is a physician before relying on the longer 180 days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUMANA MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 months from the processed date to file an appeal. Humana's published escalation ladder then runs on top: level 2 appeal 60 days from the level 1 denial, level 3 four months from the level 2 denial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplied by the practice for Humana Gold Plus HMO. Humana publishes the level 2 and level 3 timers (provider.humana.com/coverage-claims/payment-integrity/reconsiderations-appeals) but not the level 1 filing window, which is set by the plan or the provider agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humana Gold Plus HMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same initial filing split as Humana commercial - column C carries the 90 day ancillary figure, so confirm the rendering provider is a physician before relying on 180 days. The appeal window is the opposite story and the longest on this sheet: 18 months from the processed date, against 90 days to get the claim in. A Humana Gold Plus timely filing denial is worth reviewing long after the filing window itself has closed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEDICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 days from DOS; 180 days from the Medicare payment date for Select Solution and Prime Solution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within the filing limit in the agreement, but the clock starts on the date Medica notified you the claim failed processing or was denied. Where the rejection was Medica error, up to 1 year from the Confirmation Report run date or the EOP date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the processing date. For provider liability denials, 12 months from the check date on the PRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medica - Claim Adjustment/Appeal Guidelines and Timely Filing and Late Claims Policy (partner.medica.com/providers/medica-administrative-manual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In network original claims must reach the designated claims address within 180 days of the date of service, or the discharge date for inpatient. On Medica Select Solution and Prime Solution with Medicare primary, the 180 days runs from the payment date on the explanation of Medicare benefits instead. The provider agreement can set a different limit and governs where it does.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEDICARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reopening to correct a clerical error or omission - 1 year from the date of the initial determination. Minor errors go through reopening, not the appeals process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redetermination - 120 days from receipt of the initial determination. Receipt is presumed 5 calendar days after the date on the remittance advice, so the MAC allows 125 days from the RA date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMS - Medicare Claims Processing Manual Chapter 34, Reopening and Revision of Claim Determinations; First Level of Appeal: Redetermination by a Medicare Contractor (cms.gov)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicare Part B Arizona *; DME Region D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One calendar year from the date of service, set by statute rather than by contract. Largest payer in the 2026-S1 pending file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MERCY CARE ADVANTAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 days from DOS or eligibility posting, whichever is later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resubmission is the only route - contracted providers have no claim dispute rights on this product. Mark the claim "Attention: Resubmissions" so it is not denied as a duplicate. The Advantage manual publishes no separate window, so the AHCCCS resubmission parameter of 12 months from the date of service is applied here</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 months from the date of service, applied from the AHCCCS parameter at the practice's direction. The published Advantage manual takes the opposite position - it states that contracted providers have no claim dispute rights on this product and directs a disputed claim back through resubmission - so confirm the route with Mercy Care before filing a dispute rather than a resubmission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercy Care Advantage Provider Manual, January 2026 (mercycareaz.org/providers/provider-manual.html)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercy Care Health Plan Advantage (AHCCCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New claims must be filed within 150 days of the date of service or the eligibility posting date, whichever is later - a shorter window than the 365 days Mercy Care Medicaid allows. Corrected claim and dispute windows follow the AHCCCS parameter of 12 months from the date of service, the same as Mercy Care Medicaid, applied at the practice's direction. Be aware the published Advantage manual says contracted providers have no claim dispute rights here and routes disputed claims through resubmission instead, so a dispute may be refused on that basis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MERCY CARE MEDICAID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 days from the date of service or the eligibility posting date, whichever is later. If a claim is recouped, a further 60 days from the recoupment date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim disputes: 12 months from the date of service, 12 months after the eligibility posting date, or 60 days after the date of a timely claim submission - whichever is less</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercy Care - Claims Processing Manual and Provider Manual; Claim Dispute Reminder notices (mercycareaz.org/providers/claims.html)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC); Mercy Care RBHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPTUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No separate window published. Resubmit with claim frequency code 7 and the payer claim control number; a disputed decision goes through the PDR route below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 calendar days of the payment or denial, on the Provider Dispute Resolution Request (PDR) form or through the Optum Pro portal. Outcome issued within 45 working days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optum Care - Claims Provider Manual and Arizona Provider Dispute Resolution Request form (optum.com; business.optum.com). The 365 day PDR window is Optum's standard across markets; it is published explicitly in the California AB 1455 dispute notices, not in an Arizona specific document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSCAR HEALTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No separate window - the corrected claim must land inside the 180 day filing limit from the date of service. Submit the entire claim as a replacement with frequency code 7 (CMS 1500 box 22) or type of bill xx7 (UB-04), carrying the original payer claim ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 calendar days after notice of the adverse decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscar Health - 2026 Provider Manual effective 01/01/26 and Claims Disputes Provider Form (hioscar.com/providers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscar Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REDIRECT HEALTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not documented - third party administrator, the plan document sets the limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not documented - third party administrator, the window comes from the underlying plan document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not documented - a formal claim appeal is filed on their online appeal form, but no window is published</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redirect Health - Provider Portal and claims information (redirecthealth.com). No filing windows published; claims questions to Claims@RedirectAdmin.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redirect Health Administration LLC administers self-funded plans, so the filing limit comes from the underlying plan document rather than from a single Redirect policy. A clean claim is paid within 45 business days. Claim questions go to Claims@RedirectAdmin.com; appeals are filed on their online appeal form. No filing windows are published - request them from the plan administrator.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRICARE EAST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 year from the date of service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must fall inside the 1 year claim filing deadline. A corrected claim is not an appeal and is filed separately to the corrected claims address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 days from the date on the explanation of benefits. Corrected claims are among the issues that are not appealable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humana Military - TRICARE Provider Handbook East Region and Claims pages (humanamilitary.com/provider/claims); TRICARE - How to Submit a Claim Appeal (tricare.mil)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administered by Humana Military. All claims for benefits must be filed no later than one year after the date services were provided. Note the pending file shows Tricare West and Tricare for Life, not Tricare East - confirm which region we actually bill, as the West region contractor changed on 1 January 2025.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIWEST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365 days of the last processed claim determination date. The corrected claim completely replaces the previously filed claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconsideration 90 days of the original claim processed date. Forms filed outside that window are denied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TriWest VA CCN - Billing and Claims and Provider Claims Reconsideration (vaccn.triwest.com/en/provider)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIWEST VA CCN CLAIMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TriWest administers VA Community Care Network Region 4; claims post under the same payer name as the VA CCN row below, so check which limit the claim was billed under.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UHC COMMERCIAL</t>
-  </si>
-  <si>
     <t xml:space="preserve">12 months from the date of the EOB or PRA to complete both steps: reconsideration first, then appeal</t>
   </si>
   <si>
@@ -835,10 +835,10 @@
     <t xml:space="preserve">Carriers with no limit on file</t>
   </si>
   <si>
-    <t xml:space="preserve">Three carriers are still without an initial filing limit and are shaded amber: AARP MA Choice / Medicare Complete, Redirect Health and UMR / Wausau. Redirect Health and UMR / Wausau are third party administrators, so their limits come from the underlying plan document rather than from a single carrier policy - the denial letter or EOB carries the deadline. AARP Medicare Complete is administered by UnitedHealthcare but no published limit was found for the product.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Related products are not treated as interchangeable. Mercy Care Medicaid allows 365 days to file but Mercy Care Advantage allows only 150, and the Advantage product gives contracted providers no dispute rights at all. Likewise the UHC Medicare Advantage limit of 90 days has not been copied across to AARP Medicare Complete, even though UnitedHealthcare administers it.</t>
+    <t xml:space="preserve">Two carriers are still without an initial filing limit and are shaded amber: Redirect Health and UMR / Wausau. Both are third party administrators, so their limits come from the underlying plan document rather than from a single carrier policy - the denial letter or EOB carries the deadline.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Related products are not treated as interchangeable, and two rows prove the point. Mercy Care Medicaid allows 365 days to file but Mercy Care Advantage allows only 150, and the Advantage product gives contracted providers no dispute rights. AARP Medicare Advantage from UHC AZ-0003 is administered by UnitedHealthcare but carries its own windows - 365 days to correct and 365 to appeal - where the other UHC rows carry 180 days to correct and a shared 12 month budget for the two appeal steps. Check the plan before assuming a sibling product's rule.</t>
   </si>
   <si>
     <t xml:space="preserve">Carriers with more than one limit</t>
@@ -934,7 +934,7 @@
     <t xml:space="preserve">Devoted is the sharpest contrast on the sheet between the initial and the corrected claim window: 60 days from the date of service to get the claim in, but a full year from the processed date to correct it once the payer has it. The first pass is what has to be fast.</t>
   </si>
   <si>
-    <t xml:space="preserve">UnitedHealthcare gives 12 months from the EOB or PRA to complete both steps - reconsideration first, then appeal. That is one 12 month budget covering the pair, not 12 months each. Non-contracted Medicare Advantage claims get 120 calendar days from the original claim determination instead.</t>
+    <t xml:space="preserve">UnitedHealthcare gives 12 months from the EOB or PRA to complete both steps - reconsideration first, then appeal. That is one 12 month budget covering the pair, not 12 months each, and corrected claims get 180 days from the original remittance. Non-contracted Medicare Advantage claims get 120 calendar days from the original claim determination instead. The AARP Medicare Advantage row is the exception and must not be worked to these figures: that plan carries 365 days from the processed date for corrections, reconsiderations and appeals alike.</t>
   </si>
   <si>
     <t xml:space="preserve">Aetna runs both windows from the determination date: 180 days to submit a corrected claim or reconsideration, then a further 60 days from the reconsideration decision for a formal appeal. State exceptions apply to fully insured members.</t>
@@ -970,7 +970,7 @@
     <t xml:space="preserve">Sources and method</t>
   </si>
   <si>
-    <t xml:space="preserve">Every figure in columns B-M was taken from the carrier's own provider manual, provider portal page or, for Medicare, the CMS Claims Processing Manual, with three exceptions supplied by the practice: the Devoted windows, the Humana Gold Plus HMO appeal window on the Humana MA row, and the BCBS resubmission window. Column N names the source for the corrected claim and appeal figures row by row; the initial limits came from the carrier list supplied by the practice and, where that list was blank, from the carrier document named in the notes column. No figure was carried across from a related product.</t>
+    <t xml:space="preserve">Every figure in columns B-M was taken from the carrier's own provider manual, provider portal page or, for Medicare, the CMS Claims Processing Manual, with four exceptions supplied by the practice: the Devoted windows, the Humana Gold Plus HMO appeal window on the Humana MA row, the BCBS resubmission window, and the AARP Medicare Advantage from UHC AZ-0003 (HMO-POS) figures. Column N names the source for the corrected claim and appeal figures row by row; the initial limits came from the carrier list supplied by the practice and, where that list was blank, from the carrier document named in the notes column. No figure was carried across from a related product.</t>
   </si>
   <si>
     <t xml:space="preserve">Direct document downloads were blocked in the environment this research was run from, so the figures were read from the carriers' published pages through search rather than from locally saved PDFs. Rows marked 'Verify vs manual' are the ones where the published wording was general, varied by state, or came from a document written for another market, and the Arizona specific figure should be pulled from the manual before a claim is worked against it.</t>
@@ -982,7 +982,7 @@
     <t xml:space="preserve">Corrected claim and appeal windows are contract sensitive in the same way initial filing limits are. Where a contract and a provider manual disagree, the contract governs. Re-confirm before writing off a claim as untimely.</t>
   </si>
   <si>
-    <t xml:space="preserve">Corrected claim and appeal columns compiled 12 August 2026, and the remaining initial, corrected claim and appeal gaps filled on the same date. The Devoted windows, the Humana Gold Plus HMO appeal window and the BCBS resubmission window were supplied by the practice; every other figure came from the carrier document named in column N or the notes column. No claim, patient or payment data is included in this workbook.</t>
+    <t xml:space="preserve">Corrected claim and appeal columns compiled 12 August 2026, and the remaining initial, corrected claim and appeal gaps filled on the same date. The Devoted windows, the Humana Gold Plus HMO appeal window, the BCBS resubmission window and the AARP Medicare Advantage from UHC AZ-0003 (HMO-POS) figures were supplied by the practice; every other figure came from the carrier document named in column N or the notes column. No claim, patient or payment data is included in this workbook.</t>
   </si>
 </sst>
 </file>
@@ -1100,12 +1100,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFDDEBF7"/>
       </patternFill>
@@ -1120,6 +1114,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE4DFEC"/>
         <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -1197,7 +1197,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1213,11 +1213,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1226,31 +1222,35 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1690,7 +1690,9 @@
       <c r="B5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
@@ -1701,16 +1703,16 @@
         <v>22</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>180</v>
+        <v>365</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>365</v>
@@ -1718,37 +1720,37 @@
       <c r="L5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>120</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>180</v>
@@ -1757,10 +1759,10 @@
         <v>23</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>180</v>
@@ -1769,74 +1771,74 @@
         <v>23</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>180</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>365</v>
       </c>
       <c r="L7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>20</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>120</v>
@@ -1844,23 +1846,23 @@
       <c r="D8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>24</v>
+      <c r="E8" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>49</v>
+        <v>21</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>180</v>
@@ -1868,25 +1870,25 @@
       <c r="L8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>365</v>
@@ -1894,21 +1896,21 @@
       <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>24</v>
+      <c r="E9" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>60</v>
@@ -1916,25 +1918,25 @@
       <c r="L9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>26</v>
+      <c r="M9" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>20</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>120</v>
@@ -1942,59 +1944,59 @@
       <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>24</v>
+      <c r="E10" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>365</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="P10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="13" t="n">
         <v>60</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>24</v>
+      <c r="E11" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>365</v>
@@ -2002,11 +2004,11 @@
       <c r="H11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>50</v>
+      <c r="I11" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>365</v>
@@ -2015,24 +2017,24 @@
         <v>23</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="P11" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>47</v>
+        <v>70</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>120</v>
@@ -2040,11 +2042,11 @@
       <c r="D12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>24</v>
+      <c r="E12" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>180</v>
@@ -2053,10 +2055,10 @@
         <v>23</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>180</v>
@@ -2065,53 +2067,53 @@
         <v>23</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N12" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O12" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="P12" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>77</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>78</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="16" t="s">
+      <c r="I13" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>79</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>21</v>
+      <c r="M13" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>80</v>
@@ -2127,27 +2129,27 @@
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>47</v>
+      <c r="B14" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>120</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>78</v>
+        <v>38</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="16" t="s">
-        <v>21</v>
+      <c r="I14" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>84</v>
@@ -2158,8 +2160,8 @@
       <c r="L14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M14" s="11" t="s">
-        <v>50</v>
+      <c r="M14" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>85</v>
@@ -2173,8 +2175,8 @@
       <c r="A15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>47</v>
+      <c r="B15" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>120</v>
@@ -2182,8 +2184,8 @@
       <c r="D15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>26</v>
+      <c r="E15" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>88</v>
@@ -2192,10 +2194,10 @@
         <v>365</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>89</v>
@@ -2204,10 +2206,10 @@
         <v>365</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>90</v>
@@ -2223,8 +2225,8 @@
       <c r="A16" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>47</v>
+      <c r="B16" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>120</v>
@@ -2232,8 +2234,8 @@
       <c r="D16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>26</v>
+      <c r="E16" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>88</v>
@@ -2242,10 +2244,10 @@
         <v>365</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>93</v>
@@ -2254,10 +2256,10 @@
         <v>365</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>94</v>
@@ -2273,7 +2275,7 @@
       <c r="A17" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="16" t="s">
         <v>97</v>
       </c>
       <c r="C17" s="7" t="n">
@@ -2282,8 +2284,8 @@
       <c r="D17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>24</v>
+      <c r="E17" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>98</v>
@@ -2292,10 +2294,10 @@
         <v>90</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>99</v>
@@ -2307,7 +2309,7 @@
         <v>23</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>100</v>
@@ -2323,7 +2325,7 @@
       <c r="A18" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="7" t="n">
@@ -2332,18 +2334,18 @@
       <c r="D18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="16" t="s">
+      <c r="E18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="14" t="s">
         <v>105</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="16" t="s">
-        <v>21</v>
+      <c r="I18" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>106</v>
@@ -2354,8 +2356,8 @@
       <c r="L18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M18" s="11" t="s">
-        <v>50</v>
+      <c r="M18" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>107</v>
@@ -2371,8 +2373,8 @@
       <c r="A19" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>110</v>
+      <c r="B19" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>90</v>
@@ -2380,23 +2382,23 @@
       <c r="D19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>24</v>
+      <c r="E19" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>90</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>180</v>
@@ -2405,36 +2407,36 @@
         <v>23</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="O19" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="O19" s="9" t="s">
+      <c r="P19" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>60</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>24</v>
+      <c r="E20" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>365</v>
@@ -2443,10 +2445,10 @@
         <v>23</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>90</v>
@@ -2455,98 +2457,98 @@
         <v>23</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N20" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O20" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="O20" s="9" t="s">
+      <c r="P20" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>123</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>180</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>365</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N21" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="O21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="P21" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>180</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>132</v>
+        <v>21</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>60</v>
@@ -2555,24 +2557,24 @@
         <v>23</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N22" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="O22" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="O22" s="9" t="s">
+      <c r="P22" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>136</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>137</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>90</v>
@@ -2580,23 +2582,23 @@
       <c r="D23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>138</v>
+      <c r="E23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>90</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>139</v>
+        <v>40</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>60</v>
@@ -2604,25 +2606,25 @@
       <c r="L23" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M23" s="11" t="s">
-        <v>26</v>
+      <c r="M23" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="N23" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="O23" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="O23" s="9" t="s">
+      <c r="P23" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>136</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>90</v>
@@ -2630,23 +2632,23 @@
       <c r="D24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>138</v>
+      <c r="E24" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>90</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>144</v>
+        <v>40</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="K24" s="7" t="n">
         <v>540</v>
@@ -2655,36 +2657,36 @@
         <v>23</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N24" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="O24" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="O24" s="9" t="s">
+      <c r="P24" s="9" t="s">
         <v>146</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>148</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>149</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>180</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>365</v>
@@ -2693,10 +2695,10 @@
         <v>23</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>365</v>
@@ -2705,36 +2707,36 @@
         <v>23</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N25" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="O25" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="O25" s="9" t="s">
+      <c r="P25" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>365</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>365</v>
@@ -2743,10 +2745,10 @@
         <v>23</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K26" s="7" t="n">
         <v>120</v>
@@ -2755,74 +2757,74 @@
         <v>23</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N26" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="O26" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="O26" s="9" t="s">
+      <c r="P26" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>164</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>150</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>166</v>
+        <v>40</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>365</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="N27" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="O27" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="O27" s="9" t="s">
+      <c r="P27" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>171</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>180</v>
@@ -2830,47 +2832,47 @@
       <c r="D28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>24</v>
+      <c r="E28" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>173</v>
+        <v>21</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="K28" s="7" t="n">
         <v>365</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N28" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="O28" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="P28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>177</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>90</v>
@@ -2878,11 +2880,11 @@
       <c r="D29" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>24</v>
+      <c r="E29" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>365</v>
@@ -2890,11 +2892,11 @@
       <c r="H29" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>50</v>
+      <c r="I29" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>365</v>
@@ -2902,47 +2904,47 @@
       <c r="L29" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M29" s="11" t="s">
-        <v>50</v>
+      <c r="M29" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="N29" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="O29" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="P29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>171</v>
+        <v>181</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>180</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>180</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K30" s="7" t="n">
         <v>180</v>
@@ -2950,91 +2952,91 @@
       <c r="L30" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M30" s="11" t="s">
-        <v>50</v>
+      <c r="M30" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="N30" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="O30" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="P30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>187</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>189</v>
+      <c r="E31" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>190</v>
+      <c r="I31" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M31" s="16" t="s">
-        <v>21</v>
+      <c r="M31" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>20</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>194</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>365</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>365</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K32" s="7" t="n">
         <v>90</v>
@@ -3043,24 +3045,24 @@
         <v>23</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O32" s="9" t="s">
         <v>20</v>
       </c>
       <c r="P32" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>47</v>
+        <v>198</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>120</v>
@@ -3068,11 +3070,11 @@
       <c r="D33" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>24</v>
+      <c r="E33" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>365</v>
@@ -3081,10 +3083,10 @@
         <v>23</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K33" s="7" t="n">
         <v>90</v>
@@ -3093,24 +3095,24 @@
         <v>23</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N33" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="O33" s="9" t="s">
+      <c r="P33" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>177</v>
+        <v>204</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>90</v>
@@ -3118,11 +3120,11 @@
       <c r="D34" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>24</v>
+      <c r="E34" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>180</v>
@@ -3131,7 +3133,7 @@
         <v>23</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>206</v>
@@ -3143,7 +3145,7 @@
         <v>23</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N34" s="9" t="s">
         <v>207</v>
@@ -3157,20 +3159,20 @@
       <c r="A35" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>177</v>
+      <c r="B35" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>90</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>180</v>
@@ -3179,7 +3181,7 @@
         <v>23</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>210</v>
@@ -3191,7 +3193,7 @@
         <v>23</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>211</v>
@@ -3207,8 +3209,8 @@
       <c r="A36" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>54</v>
+      <c r="B36" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>365</v>
@@ -3216,11 +3218,11 @@
       <c r="D36" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>24</v>
+      <c r="E36" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>180</v>
@@ -3229,7 +3231,7 @@
         <v>23</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>206</v>
@@ -3241,7 +3243,7 @@
         <v>23</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>207</v>
@@ -3257,8 +3259,8 @@
       <c r="A37" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>177</v>
+      <c r="B37" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>90</v>
@@ -3266,11 +3268,11 @@
       <c r="D37" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>24</v>
+      <c r="E37" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>180</v>
@@ -3279,9 +3281,9 @@
         <v>23</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="12" t="s">
         <v>218</v>
       </c>
       <c r="K37" s="7" t="n">
@@ -3291,7 +3293,7 @@
         <v>23</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N37" s="9" t="s">
         <v>219</v>
@@ -3305,25 +3307,25 @@
       <c r="A38" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>188</v>
+      <c r="B38" s="18" t="s">
+        <v>187</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="16" t="s">
+      <c r="E38" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="14" t="s">
         <v>222</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="16" t="s">
-        <v>21</v>
+      <c r="I38" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>223</v>
@@ -3334,8 +3336,8 @@
       <c r="L38" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M38" s="11" t="s">
-        <v>50</v>
+      <c r="M38" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>224</v>
@@ -3351,8 +3353,8 @@
       <c r="A39" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>171</v>
+      <c r="B39" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>180</v>
@@ -3360,11 +3362,11 @@
       <c r="D39" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>24</v>
+      <c r="E39" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>365</v>
@@ -3373,10 +3375,10 @@
         <v>23</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K39" s="7" t="n">
         <v>90</v>
@@ -3385,13 +3387,13 @@
         <v>23</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>228</v>
@@ -3401,7 +3403,7 @@
       <c r="A40" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>230</v>
       </c>
       <c r="C40" s="7" t="n">
@@ -3410,8 +3412,8 @@
       <c r="D40" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>24</v>
+      <c r="E40" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>231</v>
@@ -3423,7 +3425,7 @@
         <v>23</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>232</v>
@@ -3435,7 +3437,7 @@
         <v>23</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>233</v>
@@ -3500,7 +3502,7 @@
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$E$5:$E$40,"Confirmed")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3518,7 +3520,7 @@
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$E$5:$E$40,"Needs research")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3528,7 +3530,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$C$5:$C$40,60)</f>
@@ -3537,11 +3539,11 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B12" s="22" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$C$5:$C$40,90)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3555,7 +3557,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$C$5:$C$40,120)</f>
@@ -3573,7 +3575,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$C$5:$C$40,180)</f>
@@ -3610,7 +3612,7 @@
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">COUNTIFS('Timely Filing'!$C$5:$C$40,"&lt;=90",'Timely Filing'!$C$5:$C$40,"&gt;0")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3694,7 +3696,7 @@
       </c>
       <c r="B33" s="24" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$M$5:$M$40,"Confirmed")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3703,7 +3705,7 @@
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">COUNTIF('Timely Filing'!$M$5:$M$40,"Verify vs contract")+COUNTIF('Timely Filing'!$M$5:$M$40,"Verify vs manual")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
